--- a/astro-site/public/dl/catering-checklist-templates/05-catering-event-setup-breakdown-checklist.xlsx
+++ b/astro-site/public/dl/catering-checklist-templates/05-catering-event-setup-breakdown-checklist.xlsx
@@ -1178,7 +1178,7 @@
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>Place the chafing dishes and check the chafing fuel: they hold, they don't reheat (reheat cold food to 165 °F first, FDA Food Code 3-403.11) and keep it at 135 °F or above; keep fuel cans away from linens and decor, never refill or move a lit chafer, keep an extinguisher at hand and follow the venue's and fire marshal's open-flame rules</t>
+          <t>Place the chafing dishes and check the chafing fuel: they hold, they don't reheat (reheat cold food to 165 °F within 2 h first, FDA Food Code 3-403.11) and keep it at 135 °F or above; keep fuel cans away from linens and decor, never refill or move a lit chafer, keep an extinguisher at hand and follow the venue's and fire marshal's open-flame rules</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr">
@@ -1453,7 +1453,7 @@
   </mergeCells>
   <conditionalFormatting sqref="A6:G41">
     <cfRule type="expression" priority="1" dxfId="0">
-      <formula>$E6="✓"</formula>
+      <formula>AND($E6="✓",$B6&lt;&gt;"Task")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Handle leftovers: food that was held at 41 °F or below (or 135 °F or above) and never went out to the room: cool it (135 °F to 70 °F within 2 h, then to 41 °F within 4 h more, FDA Food Code 3-501.14), in a clean, labeled, dated container; anything that sat exposed on the buffet or was held under time as a public health control gets discarded. Log the event's waste</t>
+          <t>Handle leftovers: food that was held at 41 °F or below (or 135 °F or above) and never went out to the room: cool the hot food (135 °F to 70 °F within 2 h, then to 41 °F within 4 h more, FDA Food Code 3-501.14) and put the cold food straight back at 41 °F or below, in a clean, labeled, dated container; anything that sat exposed on the buffet or was held under time as a public health control gets discarded. Log the event's waste</t>
         </is>
       </c>
       <c r="C18" s="17" t="inlineStr">
@@ -2008,7 +2008,7 @@
   </mergeCells>
   <conditionalFormatting sqref="A6:G28">
     <cfRule type="expression" priority="1" dxfId="0">
-      <formula>$E6="✓"</formula>
+      <formula>AND($E6="✓",$B6&lt;&gt;"Task")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
